--- a/doc/_static/example-files/PMHC-5-0-treatment.xlsx
+++ b/doc/_static/example-files/PMHC-5-0-treatment.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennib/Work/git/PMHC/spec/doc/_static/example-files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E98E16-781B-8448-BB62-B71EA7640B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="28740" windowHeight="17660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
     <sheet name="SIDAS" sheetId="18" r:id="rId18"/>
     <sheet name="WHO-5" sheetId="19" r:id="rId19"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1132,8 +1138,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1170,13 +1176,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1214,7 +1228,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1248,6 +1262,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1282,9 +1297,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1457,11 +1473,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1469,7 +1485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1477,7 +1493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1491,11 +1507,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1554,7 +1570,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1610,7 +1626,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1666,7 +1682,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1722,7 +1738,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1778,7 +1794,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1834,7 +1850,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1890,7 +1906,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1946,7 +1962,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2002,7 +2018,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2058,7 +2074,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2120,11 +2136,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2141,7 +2157,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2158,7 +2174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2175,7 +2191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2192,7 +2208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2209,7 +2225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2226,7 +2242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2243,7 +2259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2260,7 +2276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2277,7 +2293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2294,7 +2310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2311,7 +2327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2328,7 +2344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2351,11 +2367,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2384,7 +2400,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2410,7 +2426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2436,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2462,7 +2478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2488,7 +2504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2514,7 +2530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2540,7 +2556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2566,7 +2582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2592,7 +2608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2618,7 +2634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2650,11 +2666,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2695,7 +2711,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2736,7 +2752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2783,11 +2799,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2804,7 +2820,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2821,7 +2837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2838,7 +2854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2855,7 +2871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2872,7 +2888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2895,11 +2911,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2916,7 +2932,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2939,11 +2955,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2960,7 +2976,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2980,11 +2996,11 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3001,7 +3017,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3015,7 +3031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3029,7 +3045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3049,11 +3065,11 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3082,7 +3098,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3108,7 +3124,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3140,11 +3156,11 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3173,7 +3189,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3199,7 +3215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3231,11 +3247,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3270,7 +3286,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3305,11 +3321,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3344,7 +3360,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3376,7 +3392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3408,7 +3424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3440,7 +3456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3472,7 +3488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -3504,7 +3520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3542,11 +3558,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AE11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -3602,10 +3618,10 @@
         <v>56</v>
       </c>
       <c r="S1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T1" t="s">
         <v>57</v>
-      </c>
-      <c r="T1" t="s">
-        <v>58</v>
       </c>
       <c r="U1" t="s">
         <v>59</v>
@@ -3641,7 +3657,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3733,7 +3749,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3789,10 +3805,10 @@
         <v>4</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3">
         <v>303</v>
@@ -3828,7 +3844,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3920,7 +3936,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3976,10 +3992,10 @@
         <v>3</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5">
         <v>402</v>
@@ -4012,7 +4028,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4104,7 +4120,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4157,10 +4173,10 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <v>205</v>
@@ -4193,7 +4209,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -4285,7 +4301,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4377,7 +4393,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4469,7 +4485,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4522,10 +4538,10 @@
         <v>1</v>
       </c>
       <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
         <v>9</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
       </c>
       <c r="U11">
         <v>102</v>
@@ -4564,11 +4580,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>91</v>
       </c>
@@ -4582,7 +4598,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4596,7 +4612,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -4610,7 +4626,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4624,7 +4640,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4638,7 +4654,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4652,7 +4668,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4666,7 +4682,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -4680,7 +4696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4694,7 +4710,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4708,7 +4724,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4728,11 +4744,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -4752,7 +4768,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4769,7 +4785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -4786,7 +4802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4803,7 +4819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4820,7 +4836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4837,7 +4853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -4854,7 +4870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -4871,7 +4887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4888,7 +4904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4905,7 +4921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -4922,7 +4938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -4939,7 +4955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -4956,7 +4972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -4973,7 +4989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -4990,7 +5006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -5007,7 +5023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -5024,7 +5040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -5041,7 +5057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -5058,7 +5074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -5075,7 +5091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -5092,7 +5108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -5115,11 +5131,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5178,7 +5194,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -5234,7 +5250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -5290,7 +5306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5346,7 +5362,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -5402,7 +5418,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -5464,11 +5480,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5500,7 +5516,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -5529,7 +5545,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -5558,7 +5574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5587,7 +5603,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -5616,7 +5632,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -5645,7 +5661,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -5674,7 +5690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -5703,7 +5719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -5732,7 +5748,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -5761,7 +5777,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5796,11 +5812,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:BB22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:54">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5964,7 +5980,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2" spans="1:54">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6125,7 +6141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:54">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6286,7 +6302,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:54">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6447,7 +6463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:54">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6608,7 +6624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:54">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -6769,7 +6785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:54">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6930,7 +6946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:54">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -7091,7 +7107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:54">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -7252,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:54">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -7413,7 +7429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7574,7 +7590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:54">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -7735,7 +7751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:54">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -7896,7 +7912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:54">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -8057,7 +8073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:54">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -8218,7 +8234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:54">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -8379,7 +8395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -8540,7 +8556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -8701,7 +8717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -8862,7 +8878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -9023,7 +9039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -9184,7 +9200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
